--- a/lite/reviews_ml.xlsx
+++ b/lite/reviews_ml.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11229"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/felix/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/felix/dev/python-for-excel-2e/src/lite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B89CCE-44E2-BA4D-8374-C787859D7D82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF23DD97-BB01-6A49-837E-BE49E86A3C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="880" yWindow="780" windowWidth="33320" windowHeight="21360" xr2:uid="{6DF24392-3798-A448-811A-D79A9ADC60F3}"/>
   </bookViews>
@@ -451,14 +451,24 @@
     <we:property name="pyodideVersion" value="&quot;0.27.5&quot;"/>
     <we:property name="addinVersion" value="&quot;1.0.0.0-19&quot;"/>
     <we:property name="requirements.txt" value="&quot;# Pin the version of packages that are installed from PyPI.\n# Don't pin the version if they are on this list:\n# https:\/\/pyodide.org\/en\/stable\/usage\/packages-in-pyodide.html\n#\n# New packages are installed on the fly.\n# However, the following situations require a restart:\n# - removing a package\n# - changing the version of a package\n# - adding an optional dependency of xlwings, e.g, polars\n\nxlwings==0.33.19  # required\npython-dotenv==1.2.1  # required\npyodide-http  # required\nblack  # required\ntransformers_js_py==0.19.10&quot;"/>
+    <we:property name="xlwingsWorkbookId" value="&quot;64c50c0c-1460-4fe5-ab30-61fb1daa8855&quot;"/>
+    <we:property name="xlwingsSettingsWorkbook" value="&quot;{\&quot;startupBehavior\&quot;:\&quot;taskpane\&quot;}&quot;"/>
   </we:properties>
   <we:bindings/>
   <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
   <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions/>
+    </a:ext>
     <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
       <we:customFunctionIdList>
-        <we:customFunctionIds>_xldudf_CLASSIFY</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_WINGMAN</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_AI</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_AI_MODELS</we:customFunctionIds>
       </we:customFunctionIdList>
+    </a:ext>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{0858819E-0033-43BF-8937-05EC82904868}">
+      <we:backgroundApp state="1" runtimeId="Taskpane.Url"/>
     </a:ext>
   </we:extLst>
 </we:webextension>
